--- a/data/b2_centro/B2 Centro 05-2026.xlsx
+++ b/data/b2_centro/B2 Centro 05-2026.xlsx
@@ -4936,52 +4936,52 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Troca de filtros das bombas</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>4073.98</v>
+        <v>2557.79</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Material de limpeza e escritório</t>
+          <t>Reparo elétrico</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>2096.07</v>
+        <v>1967.39</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46145</v>
+        <v>46147</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Salários do mês anterior</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>2606.24</v>
+        <v>77632.42999999999</v>
       </c>
     </row>
     <row r="5">
@@ -4990,34 +4990,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Salários do mês anterior</t>
+          <t>Limpeza da caixa separadora</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>78605.21000000001</v>
+        <v>2706.24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46152</v>
+        <v>46150</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Aluguel do imóvel</t>
+          <t>Seguro do posto</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>38000</v>
+        <v>1643.86</v>
       </c>
     </row>
     <row r="7">
@@ -5026,16 +5026,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sistemas e contabilidade</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sistema de automação e contabilidade</t>
+          <t>Aluguel do imóvel</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>4300</v>
+        <v>38000</v>
       </c>
     </row>
     <row r="8">
@@ -5044,34 +5044,34 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Sistemas e contabilidade</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Sistema de automação e contabilidade</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>5416.93</v>
+        <v>4300</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>46154</v>
+        <v>46152</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tarifas bancárias</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>1654.11</v>
+        <v>5301.2</v>
       </c>
     </row>
     <row r="10">
@@ -5089,25 +5089,25 @@
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>1874.79</v>
+        <v>1909.91</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
-        <v>46157</v>
+        <v>46155</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Conta de energia</t>
+          <t>Uniformes e EPI</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>13132.12</v>
+        <v>1779.42</v>
       </c>
     </row>
     <row r="12">
@@ -5116,75 +5116,75 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Energia elétrica</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Conta de energia</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>4131.81</v>
+        <v>12890.43</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>46159</v>
+        <v>46157</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>5622.66</v>
+        <v>4052.31</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46162</v>
+        <v>46159</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Encargos (INSS e FGTS)</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>27756.78</v>
+        <v>5774.46</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Reparo elétrico</t>
+          <t>Encargos (INSS e FGTS)</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>3429.56</v>
+        <v>27161.03</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
@@ -5193,11 +5193,11 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Coleta de resíduos (óleo e borra)</t>
+          <t>Tarifas bancárias</t>
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>1809</v>
+        <v>1998.12</v>
       </c>
     </row>
     <row r="17">
@@ -5215,7 +5215,7 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>5222.2</v>
+        <v>5046.08</v>
       </c>
     </row>
     <row r="18">
@@ -5233,7 +5233,7 @@
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>5680.47</v>
+        <v>5127.2</v>
       </c>
     </row>
   </sheetData>
